--- a/TestData/LV_3_TMTT0047923_TMTT0047926_TMTT0047929_VerifyJobTypesGetsDispalyedOnAddingJobTypeFiltersWhileCreatingReports.xlsx
+++ b/TestData/LV_3_TMTT0047923_TMTT0047926_TMTT0047929_VerifyJobTypesGetsDispalyedOnAddingJobTypeFiltersWhileCreatingReports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE295FCD-3F0B-4E43-92E7-EEC71C679CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320C8B12-D051-4E1C-B0A2-B614FCE88028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,7 +156,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -164,28 +164,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,8 +651,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
     </row>
